--- a/data/trans_orig/IP05A05-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP05A05-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14762</t>
+          <t>14440</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9698</t>
+          <t>10122</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21288</t>
+          <t>21119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18438</t>
+          <t>18831</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32364</t>
+          <t>32360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32578</t>
+          <t>33074</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42962</t>
+          <t>42949</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31662</t>
+          <t>32619</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44476</t>
+          <t>44847</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69244</t>
+          <t>68315</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85234</t>
+          <t>84985</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,35%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>16711</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>24558</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>39644</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20917</t>
+          <t>20825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>36048</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50185</t>
+          <t>50063</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70799</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43530</t>
+          <t>42525</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58545</t>
+          <t>58688</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46687</t>
+          <t>47461</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>64019</t>
+          <t>64450</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>92641</t>
+          <t>94497</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>116594</t>
+          <t>117911</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>56,06%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>13221</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25162</t>
+          <t>25630</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19286</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32611</t>
+          <t>32749</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36509</t>
+          <t>34888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54942</t>
+          <t>54439</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14919</t>
+          <t>14942</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27329</t>
+          <t>27332</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>20543</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32535</t>
+          <t>32999</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38658</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57226</t>
+          <t>56579</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28783</t>
+          <t>28646</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42557</t>
+          <t>41964</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29316</t>
+          <t>29780</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42324</t>
+          <t>42286</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61591</t>
+          <t>60473</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81214</t>
+          <t>80267</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,2%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17587</t>
+          <t>16501</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13170</t>
+          <t>12491</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13556</t>
+          <t>13581</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26386</t>
+          <t>27020</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11756</t>
+          <t>12025</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23909</t>
+          <t>23400</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15021</t>
+          <t>14766</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27801</t>
+          <t>27828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29175</t>
+          <t>30536</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47077</t>
+          <t>48797</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40360</t>
+          <t>39915</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>53442</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52970</t>
+          <t>52837</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83138</t>
+          <t>82665</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>103585</t>
+          <t>101989</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,05%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15726</t>
+          <t>15602</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17254</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14749</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29292</t>
+          <t>28549</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9153</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21025</t>
+          <t>20878</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22368</t>
+          <t>22740</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32932</t>
+          <t>33315</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>35778</t>
+          <t>36313</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>50821</t>
+          <t>51355</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>59,24%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17167</t>
+          <t>17274</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27744</t>
+          <t>27594</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21206</t>
+          <t>20723</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30797</t>
+          <t>30764</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46038</t>
+          <t>45793</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,82%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>14151</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26108</t>
+          <t>25590</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15101</t>
+          <t>14907</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>26492</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>32282</t>
+          <t>32431</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>49479</t>
+          <t>48554</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36341</t>
+          <t>36935</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30128</t>
+          <t>30350</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41539</t>
+          <t>41857</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>57702</t>
+          <t>59153</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>74463</t>
+          <t>75723</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>65,4%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6902</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>14129</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>44863</t>
+          <t>45342</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62459</t>
+          <t>62726</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>55712</t>
+          <t>55919</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>75026</t>
+          <t>74326</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>106737</t>
+          <t>106565</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>131861</t>
+          <t>133162</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>50,39%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>55731</t>
+          <t>55483</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>72810</t>
+          <t>73540</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>49357</t>
+          <t>49098</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>68871</t>
+          <t>67199</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>110472</t>
+          <t>109656</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>136886</t>
+          <t>136912</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,81%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15627</t>
+          <t>16285</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18177</t>
+          <t>18041</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>15395</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>29891</t>
+          <t>30082</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>36234</t>
+          <t>37040</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>54049</t>
+          <t>55861</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>33646</t>
+          <t>33720</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51643</t>
+          <t>51101</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>75903</t>
+          <t>74797</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>100403</t>
+          <t>102437</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,99%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>53531</t>
+          <t>52786</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>72134</t>
+          <t>72545</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>52566</t>
+          <t>52321</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>72733</t>
+          <t>71970</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>111560</t>
+          <t>111867</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>138343</t>
+          <t>140012</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>40908</t>
+          <t>40424</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>58972</t>
+          <t>59206</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>50217</t>
+          <t>49953</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>68633</t>
+          <t>68188</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>94247</t>
+          <t>94551</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>121018</t>
+          <t>122538</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,27%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>181875</t>
+          <t>184998</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>222101</t>
+          <t>223248</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>201392</t>
+          <t>199954</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>238770</t>
+          <t>239758</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>396081</t>
+          <t>390977</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>452505</t>
+          <t>448218</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>325203</t>
+          <t>323204</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>367357</t>
+          <t>365301</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>337960</t>
+          <t>339142</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>380237</t>
+          <t>380793</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>675488</t>
+          <t>678822</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>736998</t>
+          <t>740350</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,88%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>115426</t>
+          <t>113549</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>151137</t>
+          <t>148841</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,47 +4622,47 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
+          <t>16,71%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>21,91%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>140349</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>122456</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>157361</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>19,47%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
           <t>16,99%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>22,25%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>140349</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>122813</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>157003</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>19,47%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>17,04%</t>
-        </is>
-      </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>247392</t>
+          <t>248684</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>295825</t>
+          <t>295430</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19092</t>
+          <t>18744</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31400</t>
+          <t>30151</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20501</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33399</t>
+          <t>33292</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42186</t>
+          <t>42274</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60560</t>
+          <t>60935</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,85%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23693</t>
+          <t>24602</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35938</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25677</t>
+          <t>25718</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39055</t>
+          <t>39043</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53389</t>
+          <t>54083</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72283</t>
+          <t>71997</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>58,9%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>706</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2443</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>10598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14394</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23650</t>
+          <t>23247</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38701</t>
+          <t>39479</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23554</t>
+          <t>23928</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38898</t>
+          <t>38990</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51643</t>
+          <t>51434</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73421</t>
+          <t>72899</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43877</t>
+          <t>42679</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60092</t>
+          <t>59703</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50461</t>
+          <t>49098</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66500</t>
+          <t>66564</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>99105</t>
+          <t>97900</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>121911</t>
+          <t>121971</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,5%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15807</t>
+          <t>15715</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28897</t>
+          <t>28738</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15873</t>
+          <t>16117</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29024</t>
+          <t>29089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35587</t>
+          <t>34678</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53878</t>
+          <t>53653</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>11856</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7968</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19760</t>
+          <t>20438</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26639</t>
+          <t>26534</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40244</t>
+          <t>40513</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35533</t>
+          <t>35718</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49071</t>
+          <t>49078</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66830</t>
+          <t>67060</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85147</t>
+          <t>86751</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>62,22%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21901</t>
+          <t>20736</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35260</t>
+          <t>34876</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16132</t>
+          <t>16186</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28352</t>
+          <t>28276</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40415</t>
+          <t>40778</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59302</t>
+          <t>59002</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,32%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24639</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38513</t>
+          <t>38705</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25570</t>
+          <t>25983</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40959</t>
+          <t>41369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54676</t>
+          <t>54717</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75345</t>
+          <t>74943</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,84%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27742</t>
+          <t>28418</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42024</t>
+          <t>42768</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28701</t>
+          <t>29301</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44657</t>
+          <t>43835</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60308</t>
+          <t>62173</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82037</t>
+          <t>82606</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,63%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6358</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16659</t>
+          <t>16932</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7670</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19081</t>
+          <t>18644</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16806</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31528</t>
+          <t>31509</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>14020</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11069</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22762</t>
+          <t>23325</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>11972</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23257</t>
+          <t>23456</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>23338</t>
+          <t>22326</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38362</t>
+          <t>36769</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17450</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28236</t>
+          <t>28581</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17374</t>
+          <t>16714</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29136</t>
+          <t>28274</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36622</t>
+          <t>37055</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53611</t>
+          <t>52825</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,27%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11172</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>9832</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16510</t>
+          <t>16343</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23681</t>
+          <t>24167</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36100</t>
+          <t>36740</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22931</t>
+          <t>22357</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36230</t>
+          <t>35997</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>50393</t>
+          <t>49336</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>68072</t>
+          <t>68009</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,51%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14425</t>
+          <t>14017</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25979</t>
+          <t>25985</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19632</t>
+          <t>20267</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32466</t>
+          <t>33437</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>37930</t>
+          <t>38305</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>54726</t>
+          <t>55789</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>48,0%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19664</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35888</t>
+          <t>34237</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>13460</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>28208</t>
+          <t>28285</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36947</t>
+          <t>36806</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>57351</t>
+          <t>57716</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>59204</t>
+          <t>58910</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>78969</t>
+          <t>78906</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>77226</t>
+          <t>76844</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>96155</t>
+          <t>97402</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>141323</t>
+          <t>140542</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>171199</t>
+          <t>169820</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>59,7%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>34371</t>
+          <t>34188</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>51702</t>
+          <t>52447</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>30369</t>
+          <t>29965</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>49358</t>
+          <t>48704</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>69036</t>
+          <t>69770</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>94892</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>91153</t>
+          <t>91710</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>110763</t>
+          <t>111154</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>89366</t>
+          <t>89775</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>110195</t>
+          <t>110516</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>186595</t>
+          <t>188306</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>215023</t>
+          <t>216309</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,67%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>28843</t>
+          <t>29330</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>46383</t>
+          <t>47166</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>55476</t>
+          <t>54840</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>69307</t>
+          <t>69683</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>96054</t>
+          <t>95248</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>17527</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>31941</t>
+          <t>32575</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>18977</t>
+          <t>19670</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>34485</t>
+          <t>34778</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>41213</t>
+          <t>39974</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>63086</t>
+          <t>60680</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>216955</t>
+          <t>216147</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>257434</t>
+          <t>257005</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>209951</t>
+          <t>207304</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>251673</t>
+          <t>248364</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>434606</t>
+          <t>438833</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>492009</t>
+          <t>497001</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>277893</t>
+          <t>280953</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>321051</t>
+          <t>323387</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>322864</t>
+          <t>327484</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>369822</t>
+          <t>371013</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>620186</t>
+          <t>620180</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>678075</t>
+          <t>683128</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,68%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>153685</t>
+          <t>154053</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>190977</t>
+          <t>193515</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>156540</t>
+          <t>156655</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>195624</t>
+          <t>195820</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>322924</t>
+          <t>320982</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>376364</t>
+          <t>375092</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21744</t>
+          <t>22275</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33786</t>
+          <t>34420</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22010</t>
+          <t>22091</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35761</t>
+          <t>35027</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46878</t>
+          <t>47533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65728</t>
+          <t>66556</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16219</t>
+          <t>16037</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27736</t>
+          <t>27949</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>18665</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31068</t>
+          <t>30564</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36941</t>
+          <t>37792</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54924</t>
+          <t>55321</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,41%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>12842</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17639</t>
+          <t>18440</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13809</t>
+          <t>13377</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25945</t>
+          <t>27109</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14628</t>
+          <t>14993</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28239</t>
+          <t>27665</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27621</t>
+          <t>27252</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31895</t>
+          <t>32213</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49871</t>
+          <t>51153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41157</t>
+          <t>41425</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58140</t>
+          <t>57378</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40277</t>
+          <t>39475</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56505</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>85531</t>
+          <t>85854</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>108768</t>
+          <t>108132</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25843</t>
+          <t>26355</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42202</t>
+          <t>42136</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34477</t>
+          <t>34434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51107</t>
+          <t>50778</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65401</t>
+          <t>64587</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87780</t>
+          <t>86957</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,59%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20506</t>
+          <t>20552</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9556</t>
+          <t>9198</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20697</t>
+          <t>20669</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20910</t>
+          <t>20591</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37439</t>
+          <t>36952</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31620</t>
+          <t>31883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45551</t>
+          <t>45495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29320</t>
+          <t>30301</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43721</t>
+          <t>43942</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65647</t>
+          <t>65918</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85258</t>
+          <t>85507</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,53%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20851</t>
+          <t>20313</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13377</t>
+          <t>13365</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25632</t>
+          <t>25477</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25291</t>
+          <t>25953</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42693</t>
+          <t>42033</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,74%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30051</t>
+          <t>31103</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44480</t>
+          <t>45100</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31404</t>
+          <t>32317</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47006</t>
+          <t>47646</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67026</t>
+          <t>66711</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88199</t>
+          <t>87841</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,2%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23792</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38284</t>
+          <t>37475</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19052</t>
+          <t>20092</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34329</t>
+          <t>33469</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46437</t>
+          <t>47358</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67457</t>
+          <t>68164</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,61%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12241</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21057</t>
+          <t>20969</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15382</t>
+          <t>15204</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31149</t>
+          <t>30802</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>23434</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33952</t>
+          <t>33737</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23938</t>
+          <t>23829</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>34736</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51030</t>
+          <t>52115</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65901</t>
+          <t>66744</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>74,34%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13426</t>
+          <t>13872</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14443</t>
+          <t>14914</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12640</t>
+          <t>12272</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25057</t>
+          <t>24737</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>9830</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11890</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7766</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>18205</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18102</t>
+          <t>18241</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18534</t>
+          <t>19633</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>19485</t>
+          <t>19522</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34735</t>
+          <t>35162</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20607</t>
+          <t>20852</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32612</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23773</t>
+          <t>23075</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36500</t>
+          <t>36182</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>47594</t>
+          <t>48713</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>65930</t>
+          <t>65857</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,79%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20995</t>
+          <t>20849</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20626</t>
+          <t>20617</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21920</t>
+          <t>21845</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38336</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31353</t>
+          <t>31709</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49226</t>
+          <t>49314</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>31156</t>
+          <t>31582</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>49074</t>
+          <t>49819</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>67907</t>
+          <t>68240</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>92568</t>
+          <t>91932</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>58166</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>77730</t>
+          <t>75658</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>64346</t>
+          <t>64269</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>83795</t>
+          <t>83458</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>126607</t>
+          <t>127014</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>153942</t>
+          <t>154387</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,96%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22384</t>
+          <t>22664</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>38632</t>
+          <t>38724</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>22889</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>38367</t>
+          <t>38824</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>49309</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>71056</t>
+          <t>71040</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>78064</t>
+          <t>78040</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>97352</t>
+          <t>98067</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>79577</t>
+          <t>79586</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>100596</t>
+          <t>100479</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>163165</t>
+          <t>163702</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>191751</t>
+          <t>193209</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,79%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>32372</t>
+          <t>31772</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>48988</t>
+          <t>49007</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>34343</t>
+          <t>33246</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>52002</t>
+          <t>51542</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>70351</t>
+          <t>69320</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>95601</t>
+          <t>95051</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>28156</t>
+          <t>27408</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>44223</t>
+          <t>43760</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>30916</t>
+          <t>30521</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>47470</t>
+          <t>47085</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>62999</t>
+          <t>62739</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>87550</t>
+          <t>86484</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>249014</t>
+          <t>248773</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>290055</t>
+          <t>292226</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>253670</t>
+          <t>252629</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>297778</t>
+          <t>296964</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>516380</t>
+          <t>515515</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>575268</t>
+          <t>575406</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,79%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>262204</t>
+          <t>261132</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>303627</t>
+          <t>302847</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>270102</t>
+          <t>270678</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>313867</t>
+          <t>314509</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>546295</t>
+          <t>543964</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>604179</t>
+          <t>603837</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,76%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>133926</t>
+          <t>133665</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>168328</t>
+          <t>167702</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>158460</t>
+          <t>158795</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>196834</t>
+          <t>196631</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>301096</t>
+          <t>301763</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>352918</t>
+          <t>351347</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45607</t>
+          <t>45299</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69693</t>
+          <t>69364</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68385</t>
+          <t>68699</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77092</t>
+          <t>77044</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>115329</t>
+          <t>115931</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144469</t>
+          <t>144665</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27218</t>
+          <t>27741</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>579</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34082</t>
+          <t>31685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -13984,7 +13984,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>917</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32391</t>
+          <t>29898</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91231</t>
+          <t>91272</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84614</t>
+          <t>83196</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>104135</t>
+          <t>102933</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100672</t>
+          <t>105040</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>187312</t>
+          <t>187159</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,32%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26059</t>
+          <t>26329</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>91411</t>
+          <t>93844</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19240</t>
+          <t>19302</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36675</t>
+          <t>37353</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>52990</t>
+          <t>51914</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>148300</t>
+          <t>138425</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>54,23%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14722</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10964</t>
+          <t>11330</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21261</t>
+          <t>21244</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37707</t>
+          <t>37732</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47993</t>
+          <t>48715</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44851</t>
+          <t>44892</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56354</t>
+          <t>56437</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>84586</t>
+          <t>86333</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>101240</t>
+          <t>101607</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>81,01%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11259</t>
+          <t>11753</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12586</t>
+          <t>13384</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>20267</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>12791</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11003</t>
+          <t>10796</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23756</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52476</t>
+          <t>52817</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63813</t>
+          <t>63519</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54382</t>
+          <t>54622</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70491</t>
+          <t>70457</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111750</t>
+          <t>111684</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>131181</t>
+          <t>131125</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,43%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>13773</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16060</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25941</t>
+          <t>25600</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>829</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12465</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15640</t>
+          <t>16227</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31854</t>
+          <t>31658</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35191</t>
+          <t>35175</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40104</t>
+          <t>40097</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68600</t>
+          <t>68787</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74077</t>
+          <t>74075</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -15695,7 +15695,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15710,7 +15710,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>572</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>583</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -15843,7 +15843,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15858,7 +15858,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15878,7 +15878,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36048</t>
+          <t>35884</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43129</t>
+          <t>43498</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49722</t>
+          <t>49688</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54734</t>
+          <t>54911</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>88052</t>
+          <t>88587</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>96790</t>
+          <t>96867</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7015</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16186,7 +16186,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>696</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16279,7 +16279,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2321</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>64156</t>
+          <t>63795</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>83356</t>
+          <t>82467</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>77068</t>
+          <t>74939</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>103221</t>
+          <t>101635</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>146846</t>
+          <t>145499</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>178025</t>
+          <t>177734</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,9%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18846</t>
+          <t>19146</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>33095</t>
+          <t>34808</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>26794</t>
+          <t>27682</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>49248</t>
+          <t>50733</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>50186</t>
+          <t>51088</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>77494</t>
+          <t>77558</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>17154</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33004</t>
+          <t>31789</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20008</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>39029</t>
+          <t>38629</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>40591</t>
+          <t>41091</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>65758</t>
+          <t>68010</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>108295</t>
+          <t>107939</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>121124</t>
+          <t>121013</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>128177</t>
+          <t>127839</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>143465</t>
+          <t>142665</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>241252</t>
+          <t>240211</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>260391</t>
+          <t>260313</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,26%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>17980</t>
+          <t>18436</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>22316</t>
+          <t>23361</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>19097</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>36617</t>
+          <t>36497</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9013</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>9593</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>16182</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>431590</t>
+          <t>433761</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>525962</t>
+          <t>527522</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>580265</t>
+          <t>579026</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>622231</t>
+          <t>622807</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1031056</t>
+          <t>1032372</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1135895</t>
+          <t>1132857</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>87395</t>
+          <t>86040</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>191695</t>
+          <t>194931</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>84286</t>
+          <t>82847</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>119746</t>
+          <t>119506</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>181009</t>
+          <t>181538</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>301988</t>
+          <t>282317</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>39718</t>
+          <t>39649</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>63702</t>
+          <t>64793</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>46894</t>
+          <t>48013</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>74088</t>
+          <t>75794</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>91608</t>
+          <t>94428</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>129732</t>
+          <t>130997</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
